--- a/public/kk-baljooseo.xlsx
+++ b/public/kk-baljooseo.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10802"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C793578A-27DA-BF41-9829-333F221E5AD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D1FB09B-969A-AF48-B0B9-8683A5D5B668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13660" yWindow="720" windowWidth="38400" windowHeight="19060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="83">
   <si>
     <t>{{발행처로고}}</t>
   </si>
@@ -154,18 +154,10 @@
     <t>인쇄 미리보기에서 24열이 한 쪽 안에 들어가고 배율이 100%인지 보세요.</t>
   </si>
   <si>
-    <t>갑지</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>현장 정보</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>케이산업 부속</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>시공팀</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -222,46 +214,14 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>{{부속.개수}}</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>{{현장주소}}</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>{{시공팀}}</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{시공일}}</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>{{발주담당자}}</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>{{출입정보}}</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{연락처}}</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{부속}}</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{시공팀요청}}</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{케이산업요청}}</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>글자</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -294,6 +254,54 @@
   </si>
   <si>
     <t>발행처로고</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>발주서</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>발주일</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>배송요청일</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>발주처</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>발주내역</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{발주일}}</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{배송요청일}}</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{발주처}}</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>수량</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>비고</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{부속.수량}}</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{부속.비고}}</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -431,7 +439,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -455,11 +463,43 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="thin">
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
@@ -474,7 +514,7 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
@@ -486,13 +526,28 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -501,28 +556,13 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -531,28 +571,11 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
+      <right/>
+      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -561,9 +584,7 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -573,12 +594,8 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -588,23 +605,60 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -617,7 +671,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -637,24 +691,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -674,9 +722,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -690,83 +735,68 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1107,14 +1137,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD43"/>
+  <dimension ref="A1:AC37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="24" width="4" customWidth="1"/>
     <col min="26" max="26" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="24" customHeight="1">
+    <row r="1" spans="1:29" ht="24" customHeight="1">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1122,957 +1152,778 @@
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
-      <c r="F1" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
-      <c r="P1" s="18"/>
-      <c r="Q1" s="18"/>
-      <c r="R1" s="18"/>
-      <c r="S1" s="18"/>
-      <c r="T1" s="19"/>
-      <c r="U1" s="19"/>
-      <c r="V1" s="19"/>
-      <c r="W1" s="19"/>
-      <c r="X1" s="19"/>
+      <c r="F1" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
+      <c r="S1" s="16"/>
+      <c r="T1" s="17"/>
+      <c r="U1" s="17"/>
+      <c r="V1" s="17"/>
+      <c r="W1" s="17"/>
+      <c r="X1" s="17"/>
       <c r="Z1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:30" ht="24" customHeight="1">
+    <row r="2" spans="1:29" ht="24" customHeight="1">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18"/>
-      <c r="N2" s="18"/>
-      <c r="O2" s="18"/>
-      <c r="P2" s="18"/>
-      <c r="Q2" s="18"/>
-      <c r="R2" s="18"/>
-      <c r="S2" s="18"/>
-      <c r="T2" s="19"/>
-      <c r="U2" s="19"/>
-      <c r="V2" s="19"/>
-      <c r="W2" s="19"/>
-      <c r="X2" s="19"/>
-    </row>
-    <row r="3" spans="1:30" s="7" customFormat="1" ht="24" customHeight="1" thickBot="1">
-      <c r="A3" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="15"/>
-      <c r="O3" s="15"/>
-      <c r="P3" s="15"/>
-      <c r="Q3" s="15"/>
-      <c r="R3" s="15"/>
-      <c r="S3" s="15"/>
-      <c r="T3" s="15"/>
-      <c r="U3" s="15"/>
-      <c r="V3" s="15"/>
-      <c r="W3" s="15"/>
-      <c r="X3" s="15"/>
-    </row>
-    <row r="4" spans="1:30" s="7" customFormat="1" ht="24" customHeight="1">
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
+      <c r="R2" s="16"/>
+      <c r="S2" s="16"/>
+      <c r="T2" s="17"/>
+      <c r="U2" s="17"/>
+      <c r="V2" s="17"/>
+      <c r="W2" s="17"/>
+      <c r="X2" s="17"/>
+    </row>
+    <row r="3" spans="1:29" s="7" customFormat="1" ht="24" customHeight="1" thickBot="1">
+      <c r="A3" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
+      <c r="R3" s="13"/>
+      <c r="S3" s="13"/>
+      <c r="T3" s="13"/>
+      <c r="U3" s="13"/>
+      <c r="V3" s="13"/>
+      <c r="W3" s="13"/>
+      <c r="X3" s="13"/>
+    </row>
+    <row r="4" spans="1:29" s="7" customFormat="1" ht="24" customHeight="1">
       <c r="A4" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
-      <c r="E4" s="37" t="s">
-        <v>63</v>
-      </c>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="37"/>
-      <c r="J4" s="37"/>
-      <c r="K4" s="37"/>
-      <c r="L4" s="37"/>
-      <c r="M4" s="37"/>
-      <c r="N4" s="37"/>
-      <c r="O4" s="37"/>
-      <c r="P4" s="37"/>
-      <c r="Q4" s="37"/>
-      <c r="R4" s="37"/>
-      <c r="S4" s="37"/>
-      <c r="T4" s="37"/>
-      <c r="U4" s="37"/>
-      <c r="V4" s="37"/>
-      <c r="W4" s="37"/>
-      <c r="X4" s="38"/>
-    </row>
-    <row r="5" spans="1:30" s="7" customFormat="1" ht="24" customHeight="1">
+      <c r="E4" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="32"/>
+      <c r="K4" s="32"/>
+      <c r="L4" s="32"/>
+      <c r="M4" s="32"/>
+      <c r="N4" s="32"/>
+      <c r="O4" s="32"/>
+      <c r="P4" s="32"/>
+      <c r="Q4" s="32"/>
+      <c r="R4" s="32"/>
+      <c r="S4" s="32"/>
+      <c r="T4" s="32"/>
+      <c r="U4" s="32"/>
+      <c r="V4" s="32"/>
+      <c r="W4" s="32"/>
+      <c r="X4" s="33"/>
+    </row>
+    <row r="5" spans="1:29" s="7" customFormat="1" ht="24" customHeight="1">
       <c r="A5" s="11" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
-      <c r="E5" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="36"/>
-      <c r="K5" s="36"/>
-      <c r="L5" s="36"/>
+      <c r="E5" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="31"/>
       <c r="M5" s="12" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="N5" s="12"/>
       <c r="O5" s="12"/>
       <c r="P5" s="12"/>
-      <c r="Q5" s="36" t="s">
-        <v>65</v>
-      </c>
-      <c r="R5" s="36"/>
-      <c r="S5" s="36"/>
-      <c r="T5" s="36"/>
-      <c r="U5" s="36"/>
-      <c r="V5" s="36"/>
-      <c r="W5" s="36"/>
-      <c r="X5" s="40"/>
+      <c r="Q5" s="31" t="s">
+        <v>77</v>
+      </c>
+      <c r="R5" s="31"/>
+      <c r="S5" s="31"/>
+      <c r="T5" s="31"/>
+      <c r="U5" s="31"/>
+      <c r="V5" s="31"/>
+      <c r="W5" s="31"/>
+      <c r="X5" s="34"/>
       <c r="Z5" s="8"/>
     </row>
-    <row r="6" spans="1:30" s="7" customFormat="1" ht="24" customHeight="1">
+    <row r="6" spans="1:29" s="7" customFormat="1" ht="24" customHeight="1">
       <c r="A6" s="11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
       <c r="D6" s="12"/>
-      <c r="E6" s="36" t="s">
-        <v>66</v>
-      </c>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="36"/>
-      <c r="K6" s="36"/>
-      <c r="L6" s="36"/>
+      <c r="E6" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
       <c r="M6" s="12" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="N6" s="12"/>
       <c r="O6" s="12"/>
       <c r="P6" s="12"/>
-      <c r="Q6" s="36" t="s">
-        <v>67</v>
-      </c>
-      <c r="R6" s="36"/>
-      <c r="S6" s="36"/>
-      <c r="T6" s="36"/>
-      <c r="U6" s="36"/>
-      <c r="V6" s="36"/>
-      <c r="W6" s="36"/>
-      <c r="X6" s="40"/>
-    </row>
-    <row r="7" spans="1:30" s="7" customFormat="1" ht="24" customHeight="1" thickBot="1">
-      <c r="A7" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="39" t="s">
-        <v>68</v>
-      </c>
-      <c r="F7" s="39"/>
-      <c r="G7" s="39"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="39"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="39"/>
-      <c r="M7" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="N7" s="14"/>
-      <c r="O7" s="14"/>
-      <c r="P7" s="14"/>
-      <c r="Q7" s="39" t="s">
-        <v>69</v>
-      </c>
-      <c r="R7" s="39"/>
-      <c r="S7" s="39"/>
-      <c r="T7" s="39"/>
-      <c r="U7" s="39"/>
-      <c r="V7" s="39"/>
-      <c r="W7" s="39"/>
-      <c r="X7" s="41"/>
+      <c r="Q6" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="R6" s="31"/>
+      <c r="S6" s="31"/>
+      <c r="T6" s="31"/>
+      <c r="U6" s="31"/>
+      <c r="V6" s="31"/>
+      <c r="W6" s="31"/>
+      <c r="X6" s="34"/>
+    </row>
+    <row r="7" spans="1:29" s="7" customFormat="1" ht="24" customHeight="1">
+      <c r="A7" s="23"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="24"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="24"/>
+      <c r="M7" s="24"/>
+      <c r="N7" s="24"/>
+      <c r="O7" s="24"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="24"/>
+      <c r="R7" s="24"/>
+      <c r="S7" s="24"/>
+      <c r="T7" s="24"/>
+      <c r="U7" s="24"/>
+      <c r="V7" s="24"/>
+      <c r="W7" s="24"/>
+      <c r="X7" s="24"/>
       <c r="AC7" s="8"/>
     </row>
-    <row r="8" spans="1:30" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A8" s="26"/>
-      <c r="B8" s="26"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
-      <c r="I8" s="27"/>
-      <c r="J8" s="27"/>
-      <c r="K8" s="27"/>
-      <c r="L8" s="27"/>
-      <c r="M8" s="27"/>
-      <c r="N8" s="27"/>
-      <c r="O8" s="27"/>
-      <c r="P8" s="27"/>
-      <c r="Q8" s="27"/>
-      <c r="R8" s="27"/>
-      <c r="S8" s="27"/>
-      <c r="T8" s="27"/>
-      <c r="U8" s="27"/>
-      <c r="V8" s="27"/>
-      <c r="W8" s="27"/>
-      <c r="X8" s="27"/>
-      <c r="AC8" s="8"/>
-    </row>
-    <row r="9" spans="1:30" s="7" customFormat="1" ht="24" customHeight="1" thickBot="1">
-      <c r="A9" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="15"/>
-      <c r="O9" s="15"/>
-      <c r="P9" s="15"/>
-      <c r="Q9" s="15"/>
-      <c r="R9" s="15"/>
-      <c r="S9" s="15"/>
-      <c r="T9" s="15"/>
-      <c r="U9" s="15"/>
-      <c r="V9" s="15"/>
-      <c r="W9" s="15"/>
-      <c r="X9" s="15"/>
-    </row>
-    <row r="10" spans="1:30" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A10" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31" t="s">
+    <row r="8" spans="1:29" s="7" customFormat="1" ht="24" customHeight="1" thickBot="1">
+      <c r="A8" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="13"/>
+      <c r="S8" s="13"/>
+      <c r="T8" s="13"/>
+      <c r="U8" s="13"/>
+      <c r="V8" s="13"/>
+      <c r="W8" s="13"/>
+      <c r="X8" s="13"/>
+    </row>
+    <row r="9" spans="1:29" s="7" customFormat="1" ht="24" customHeight="1">
+      <c r="A9" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="28"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="35" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="36"/>
+      <c r="K9" s="36"/>
+      <c r="L9" s="36"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="37"/>
+      <c r="O9" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="P9" s="37"/>
+      <c r="Q9" s="35" t="s">
+        <v>80</v>
+      </c>
+      <c r="R9" s="36"/>
+      <c r="S9" s="36"/>
+      <c r="T9" s="36"/>
+      <c r="U9" s="36"/>
+      <c r="V9" s="36"/>
+      <c r="W9" s="36"/>
+      <c r="X9" s="38"/>
+      <c r="Z9" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" s="15" customFormat="1" ht="24" customHeight="1" thickBot="1">
+      <c r="A10" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="31"/>
-      <c r="K10" s="31"/>
-      <c r="L10" s="31"/>
-      <c r="M10" s="31"/>
-      <c r="N10" s="31"/>
-      <c r="O10" s="31"/>
-      <c r="P10" s="31"/>
-      <c r="Q10" s="31"/>
-      <c r="R10" s="31"/>
-      <c r="S10" s="31"/>
-      <c r="T10" s="31"/>
-      <c r="U10" s="31" t="s">
-        <v>56</v>
-      </c>
-      <c r="V10" s="31"/>
-      <c r="W10" s="31"/>
-      <c r="X10" s="32"/>
-      <c r="Z10" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:30" s="17" customFormat="1" ht="24" customHeight="1" thickBot="1">
-      <c r="A11" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="39" t="s">
-        <v>61</v>
-      </c>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="39"/>
-      <c r="J11" s="39"/>
-      <c r="K11" s="39"/>
-      <c r="L11" s="39"/>
-      <c r="M11" s="39"/>
-      <c r="N11" s="39"/>
-      <c r="O11" s="39"/>
-      <c r="P11" s="39"/>
-      <c r="Q11" s="39"/>
-      <c r="R11" s="39"/>
-      <c r="S11" s="39"/>
-      <c r="T11" s="39"/>
-      <c r="U11" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="V11" s="34"/>
-      <c r="W11" s="34"/>
-      <c r="X11" s="35"/>
-      <c r="Z11" s="17" t="s">
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="39"/>
+      <c r="K10" s="39"/>
+      <c r="L10" s="39"/>
+      <c r="M10" s="39"/>
+      <c r="N10" s="40"/>
+      <c r="O10" s="44" t="s">
+        <v>81</v>
+      </c>
+      <c r="P10" s="45"/>
+      <c r="Q10" s="41" t="s">
+        <v>82</v>
+      </c>
+      <c r="R10" s="42"/>
+      <c r="S10" s="42"/>
+      <c r="T10" s="42"/>
+      <c r="U10" s="42"/>
+      <c r="V10" s="42"/>
+      <c r="W10" s="42"/>
+      <c r="X10" s="43"/>
+      <c r="Z10" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="AB11" s="16"/>
-      <c r="AC11" s="16"/>
-    </row>
-    <row r="12" spans="1:30" s="17" customFormat="1" ht="24" customHeight="1">
-      <c r="A12" s="24"/>
-      <c r="B12" s="24"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="25"/>
-      <c r="I12" s="25"/>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="L12" s="25"/>
-      <c r="M12" s="25"/>
-      <c r="N12" s="25"/>
-      <c r="O12" s="25"/>
-      <c r="P12" s="25"/>
-      <c r="Q12" s="25"/>
-      <c r="R12" s="25"/>
-      <c r="S12" s="25"/>
-      <c r="T12" s="25"/>
-      <c r="U12" s="24"/>
-      <c r="V12" s="24"/>
-      <c r="W12" s="24"/>
-      <c r="X12" s="24"/>
-      <c r="AB12" s="16"/>
-      <c r="AC12" s="16"/>
-    </row>
-    <row r="13" spans="1:30" s="17" customFormat="1" ht="24" customHeight="1" thickBot="1">
-      <c r="A13" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="N13" s="15"/>
-      <c r="O13" s="15"/>
-      <c r="P13" s="15"/>
-      <c r="Q13" s="15"/>
-      <c r="R13" s="15"/>
-      <c r="S13" s="15"/>
-      <c r="T13" s="15"/>
-      <c r="U13" s="15"/>
-      <c r="V13" s="15"/>
-      <c r="W13" s="15"/>
-      <c r="X13" s="15"/>
-      <c r="AB13" s="16"/>
-      <c r="AC13" s="16"/>
-    </row>
-    <row r="14" spans="1:30" s="17" customFormat="1" ht="24" customHeight="1">
-      <c r="A14" s="42" t="s">
-        <v>70</v>
-      </c>
-      <c r="B14" s="43"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
-      <c r="J14" s="43"/>
-      <c r="K14" s="43"/>
-      <c r="L14" s="44"/>
-      <c r="M14" s="42" t="s">
-        <v>71</v>
-      </c>
-      <c r="N14" s="43"/>
-      <c r="O14" s="43"/>
-      <c r="P14" s="43"/>
-      <c r="Q14" s="43"/>
-      <c r="R14" s="43"/>
-      <c r="S14" s="43"/>
-      <c r="T14" s="43"/>
-      <c r="U14" s="43"/>
-      <c r="V14" s="43"/>
-      <c r="W14" s="43"/>
-      <c r="X14" s="51"/>
-    </row>
-    <row r="15" spans="1:30" s="17" customFormat="1" ht="24" customHeight="1">
-      <c r="A15" s="45"/>
-      <c r="B15" s="46"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="46"/>
-      <c r="E15" s="46"/>
-      <c r="F15" s="46"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="46"/>
-      <c r="I15" s="46"/>
-      <c r="J15" s="46"/>
-      <c r="K15" s="46"/>
-      <c r="L15" s="47"/>
-      <c r="M15" s="45"/>
-      <c r="N15" s="46"/>
-      <c r="O15" s="46"/>
-      <c r="P15" s="46"/>
-      <c r="Q15" s="46"/>
-      <c r="R15" s="46"/>
-      <c r="S15" s="46"/>
-      <c r="T15" s="46"/>
-      <c r="U15" s="46"/>
-      <c r="V15" s="46"/>
-      <c r="W15" s="46"/>
-      <c r="X15" s="52"/>
-      <c r="AD15" s="22"/>
-    </row>
-    <row r="16" spans="1:30" s="17" customFormat="1" ht="24" customHeight="1">
-      <c r="A16" s="45"/>
-      <c r="B16" s="46"/>
-      <c r="C16" s="46"/>
-      <c r="D16" s="46"/>
-      <c r="E16" s="46"/>
-      <c r="F16" s="46"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="46"/>
-      <c r="I16" s="46"/>
-      <c r="J16" s="46"/>
-      <c r="K16" s="46"/>
-      <c r="L16" s="47"/>
-      <c r="M16" s="45"/>
-      <c r="N16" s="46"/>
-      <c r="O16" s="46"/>
-      <c r="P16" s="46"/>
-      <c r="Q16" s="46"/>
-      <c r="R16" s="46"/>
-      <c r="S16" s="46"/>
-      <c r="T16" s="46"/>
-      <c r="U16" s="46"/>
-      <c r="V16" s="46"/>
-      <c r="W16" s="46"/>
-      <c r="X16" s="52"/>
-      <c r="AD16" s="16"/>
-    </row>
-    <row r="17" spans="1:28" s="17" customFormat="1" ht="24" customHeight="1" thickBot="1">
-      <c r="A17" s="48"/>
-      <c r="B17" s="49"/>
-      <c r="C17" s="49"/>
-      <c r="D17" s="49"/>
-      <c r="E17" s="49"/>
-      <c r="F17" s="49"/>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49"/>
-      <c r="I17" s="49"/>
-      <c r="J17" s="49"/>
-      <c r="K17" s="49"/>
-      <c r="L17" s="50"/>
-      <c r="M17" s="48"/>
-      <c r="N17" s="49"/>
-      <c r="O17" s="49"/>
-      <c r="P17" s="49"/>
-      <c r="Q17" s="49"/>
-      <c r="R17" s="49"/>
-      <c r="S17" s="49"/>
-      <c r="T17" s="49"/>
-      <c r="U17" s="49"/>
-      <c r="V17" s="49"/>
-      <c r="W17" s="49"/>
-      <c r="X17" s="53"/>
-    </row>
-    <row r="18" spans="1:28" s="17" customFormat="1" ht="24" customHeight="1">
-      <c r="A18" s="21"/>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="21"/>
-      <c r="M18" s="21"/>
-      <c r="N18" s="21"/>
-      <c r="O18" s="21"/>
-      <c r="P18" s="21"/>
-      <c r="Q18" s="21"/>
-      <c r="R18" s="21"/>
-      <c r="S18" s="21"/>
-      <c r="T18" s="21"/>
-      <c r="U18" s="21"/>
-      <c r="V18" s="21"/>
-      <c r="W18" s="21"/>
-      <c r="X18" s="21"/>
-    </row>
-    <row r="19" spans="1:28" s="17" customFormat="1" ht="24" customHeight="1">
-      <c r="A19" s="16"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="21"/>
-      <c r="N19" s="21"/>
-      <c r="O19" s="21"/>
-      <c r="P19" s="21"/>
-      <c r="Q19" s="21"/>
-      <c r="R19" s="21"/>
-      <c r="S19" s="21"/>
-      <c r="T19" s="21"/>
-      <c r="U19" s="21"/>
-      <c r="V19" s="21"/>
-      <c r="W19" s="21"/>
-      <c r="X19" s="21"/>
-    </row>
-    <row r="20" spans="1:28" s="17" customFormat="1" ht="24" customHeight="1">
-      <c r="A20" s="21"/>
-      <c r="B20" s="21"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="21"/>
-      <c r="J20" s="21"/>
-      <c r="K20" s="21"/>
-      <c r="L20" s="21"/>
-      <c r="M20" s="21"/>
-      <c r="N20" s="21"/>
-      <c r="O20" s="21"/>
-      <c r="P20" s="21"/>
-      <c r="Q20" s="21"/>
-      <c r="R20" s="21"/>
-      <c r="S20" s="21"/>
-      <c r="T20" s="21"/>
-      <c r="U20" s="21"/>
-      <c r="V20" s="21"/>
-      <c r="W20" s="21"/>
-      <c r="X20" s="21"/>
-    </row>
-    <row r="21" spans="1:28" s="17" customFormat="1" ht="24" customHeight="1">
-      <c r="A21" s="21"/>
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="21"/>
-      <c r="K21" s="21"/>
-      <c r="L21" s="21"/>
-      <c r="M21" s="21"/>
-      <c r="N21" s="21"/>
-      <c r="O21" s="21"/>
-      <c r="P21" s="21"/>
-      <c r="Q21" s="21"/>
-      <c r="R21" s="21"/>
-      <c r="S21" s="21"/>
-      <c r="T21" s="21"/>
-      <c r="U21" s="21"/>
-      <c r="V21" s="21"/>
-      <c r="W21" s="21"/>
-      <c r="X21" s="21"/>
-    </row>
-    <row r="22" spans="1:28" s="17" customFormat="1" ht="24" customHeight="1">
-      <c r="A22" s="21"/>
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="21"/>
-      <c r="K22" s="21"/>
-      <c r="L22" s="21"/>
-      <c r="M22" s="21"/>
-      <c r="N22" s="21"/>
-      <c r="O22" s="21"/>
-      <c r="P22" s="21"/>
-      <c r="Q22" s="21"/>
-      <c r="R22" s="21"/>
-      <c r="S22" s="21"/>
-      <c r="T22" s="21"/>
-      <c r="U22" s="21"/>
-      <c r="V22" s="21"/>
-      <c r="W22" s="21"/>
-      <c r="X22" s="21"/>
-    </row>
-    <row r="23" spans="1:28" s="17" customFormat="1" ht="24" customHeight="1">
-      <c r="A23" s="21"/>
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="21"/>
-      <c r="K23" s="21"/>
-      <c r="L23" s="21"/>
-      <c r="M23" s="21"/>
-      <c r="N23" s="21"/>
-      <c r="O23" s="21"/>
-      <c r="P23" s="21"/>
-      <c r="Q23" s="21"/>
-      <c r="R23" s="21"/>
-      <c r="S23" s="21"/>
-      <c r="T23" s="21"/>
-      <c r="U23" s="21"/>
-      <c r="V23" s="21"/>
-      <c r="W23" s="21"/>
-      <c r="X23" s="21"/>
-    </row>
-    <row r="24" spans="1:28" s="17" customFormat="1" ht="24" customHeight="1">
-      <c r="A24" s="21"/>
-      <c r="B24" s="21"/>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="21"/>
-      <c r="H24" s="21"/>
-      <c r="I24" s="21"/>
-      <c r="J24" s="21"/>
-      <c r="K24" s="21"/>
-      <c r="L24" s="21"/>
-      <c r="M24" s="21"/>
-      <c r="N24" s="21"/>
-      <c r="O24" s="21"/>
-      <c r="P24" s="21"/>
-      <c r="Q24" s="21"/>
-      <c r="R24" s="21"/>
-      <c r="S24" s="21"/>
-      <c r="T24" s="21"/>
-      <c r="U24" s="21"/>
-      <c r="V24" s="21"/>
-      <c r="W24" s="21"/>
-      <c r="X24" s="21"/>
-    </row>
-    <row r="25" spans="1:28" s="17" customFormat="1" ht="24" customHeight="1">
-      <c r="M25" s="21"/>
-      <c r="N25" s="21"/>
-      <c r="O25" s="21"/>
-      <c r="P25" s="21"/>
-      <c r="Q25" s="21"/>
-      <c r="R25" s="21"/>
-      <c r="S25" s="21"/>
-      <c r="T25" s="21"/>
-      <c r="U25" s="21"/>
-      <c r="V25" s="21"/>
-      <c r="W25" s="21"/>
-      <c r="X25" s="21"/>
-      <c r="AB25" s="33"/>
-    </row>
-    <row r="26" spans="1:28" s="17" customFormat="1" ht="24" customHeight="1">
-      <c r="M26" s="21"/>
-      <c r="N26" s="21"/>
-      <c r="O26" s="21"/>
-      <c r="P26" s="21"/>
-      <c r="Q26" s="21"/>
-      <c r="R26" s="21"/>
-      <c r="S26" s="21"/>
-      <c r="T26" s="21"/>
-      <c r="U26" s="21"/>
-      <c r="V26" s="21"/>
-      <c r="W26" s="21"/>
-      <c r="X26" s="21"/>
-    </row>
-    <row r="27" spans="1:28" s="17" customFormat="1" ht="24" customHeight="1">
-      <c r="M27" s="21"/>
-      <c r="N27" s="21"/>
-      <c r="O27" s="21"/>
-      <c r="P27" s="21"/>
-      <c r="Q27" s="21"/>
-      <c r="R27" s="21"/>
-      <c r="S27" s="21"/>
-      <c r="T27" s="21"/>
-      <c r="U27" s="21"/>
-      <c r="V27" s="21"/>
-      <c r="W27" s="21"/>
-      <c r="X27" s="21"/>
-    </row>
-    <row r="28" spans="1:28" s="17" customFormat="1" ht="24" customHeight="1">
-      <c r="M28" s="21"/>
-      <c r="N28" s="21"/>
-      <c r="O28" s="21"/>
-      <c r="P28" s="21"/>
-      <c r="Q28" s="21"/>
-      <c r="R28" s="21"/>
-      <c r="S28" s="21"/>
-      <c r="T28" s="21"/>
-      <c r="U28" s="21"/>
-      <c r="V28" s="21"/>
-      <c r="W28" s="21"/>
-      <c r="X28" s="21"/>
-    </row>
-    <row r="29" spans="1:28" s="17" customFormat="1" ht="24" customHeight="1">
-      <c r="M29" s="21"/>
-      <c r="N29" s="21"/>
-      <c r="O29" s="21"/>
-      <c r="P29" s="21"/>
-      <c r="Q29" s="21"/>
-      <c r="R29" s="21"/>
-      <c r="S29" s="21"/>
-      <c r="T29" s="21"/>
-      <c r="U29" s="21"/>
-      <c r="V29" s="21"/>
-      <c r="W29" s="21"/>
-      <c r="X29" s="21"/>
-    </row>
-    <row r="30" spans="1:28" s="17" customFormat="1" ht="24" customHeight="1">
-      <c r="M30" s="21"/>
-      <c r="N30" s="21"/>
-      <c r="O30" s="21"/>
-      <c r="P30" s="21"/>
-      <c r="Q30" s="21"/>
-      <c r="R30" s="21"/>
-      <c r="S30" s="21"/>
-      <c r="T30" s="21"/>
-      <c r="U30" s="21"/>
-      <c r="V30" s="21"/>
-      <c r="W30" s="21"/>
-      <c r="X30" s="21"/>
-    </row>
-    <row r="31" spans="1:28" s="17" customFormat="1" ht="24" customHeight="1"/>
-    <row r="32" spans="1:28" s="17" customFormat="1" ht="24" customHeight="1">
-      <c r="A32" s="16"/>
-      <c r="B32" s="16"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="16"/>
-      <c r="I32" s="16"/>
-      <c r="J32" s="16"/>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="16"/>
-      <c r="O32" s="16"/>
-      <c r="P32" s="16"/>
-      <c r="Q32" s="16"/>
-      <c r="R32" s="16"/>
-      <c r="S32" s="16"/>
-      <c r="T32" s="16"/>
-      <c r="U32" s="16"/>
-      <c r="V32" s="16"/>
-      <c r="W32" s="16"/>
-      <c r="X32" s="16"/>
-    </row>
-    <row r="33" spans="1:26" s="17" customFormat="1" ht="24" customHeight="1">
-      <c r="A33" s="20"/>
-      <c r="B33" s="20"/>
-      <c r="C33" s="20"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="20"/>
-      <c r="I33" s="20"/>
-      <c r="J33" s="20"/>
-      <c r="K33" s="20"/>
-      <c r="L33" s="20"/>
-      <c r="M33" s="20"/>
-      <c r="N33" s="20"/>
-      <c r="O33" s="20"/>
-      <c r="P33" s="20"/>
-      <c r="Q33" s="20"/>
-      <c r="R33" s="20"/>
-      <c r="S33" s="20"/>
-      <c r="T33" s="20"/>
-      <c r="U33" s="20"/>
-      <c r="V33" s="20"/>
-      <c r="W33" s="20"/>
-      <c r="X33" s="20"/>
-      <c r="Z33" s="23"/>
-    </row>
-    <row r="34" spans="1:26" s="17" customFormat="1" ht="24" customHeight="1"/>
-    <row r="35" spans="1:26" s="17" customFormat="1" ht="24" customHeight="1"/>
-    <row r="36" spans="1:26" s="17" customFormat="1" ht="24" customHeight="1"/>
-    <row r="37" spans="1:26" s="17" customFormat="1" ht="24" customHeight="1"/>
-    <row r="38" spans="1:26" s="17" customFormat="1" ht="24" customHeight="1"/>
-    <row r="39" spans="1:26" s="17" customFormat="1" ht="24" customHeight="1"/>
-    <row r="40" spans="1:26" s="17" customFormat="1" ht="24" customHeight="1"/>
-    <row r="41" spans="1:26" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A41" s="17"/>
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="17"/>
-      <c r="G41" s="17"/>
-      <c r="H41" s="17"/>
-      <c r="I41" s="17"/>
-      <c r="J41" s="17"/>
-      <c r="K41" s="17"/>
-      <c r="L41" s="17"/>
-      <c r="M41" s="17"/>
-      <c r="N41" s="17"/>
-      <c r="O41" s="17"/>
-      <c r="P41" s="17"/>
-      <c r="Q41" s="17"/>
-      <c r="R41" s="17"/>
-      <c r="S41" s="17"/>
-      <c r="T41" s="17"/>
-      <c r="U41" s="17"/>
-      <c r="V41" s="17"/>
-      <c r="W41" s="17"/>
-      <c r="X41" s="17"/>
-    </row>
-    <row r="42" spans="1:26" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A42" s="17"/>
-      <c r="B42" s="17"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="17"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="17"/>
-      <c r="G42" s="17"/>
-      <c r="H42" s="17"/>
-      <c r="I42" s="17"/>
-      <c r="J42" s="17"/>
-      <c r="K42" s="17"/>
-      <c r="L42" s="17"/>
-      <c r="M42" s="17"/>
-      <c r="N42" s="17"/>
-      <c r="O42" s="17"/>
-      <c r="P42" s="17"/>
-      <c r="Q42" s="17"/>
-      <c r="R42" s="17"/>
-      <c r="S42" s="17"/>
-      <c r="T42" s="17"/>
-      <c r="U42" s="17"/>
-      <c r="V42" s="17"/>
-      <c r="W42" s="17"/>
-      <c r="X42" s="17"/>
-    </row>
-    <row r="43" spans="1:26" ht="24" customHeight="1">
-      <c r="A43" s="20"/>
-      <c r="B43" s="20"/>
-      <c r="C43" s="20"/>
-      <c r="D43" s="20"/>
-      <c r="E43" s="20"/>
-      <c r="F43" s="20"/>
-      <c r="G43" s="20"/>
-      <c r="H43" s="20"/>
-      <c r="I43" s="20"/>
-      <c r="J43" s="20"/>
-      <c r="K43" s="20"/>
-      <c r="L43" s="20"/>
-      <c r="M43" s="20"/>
-      <c r="N43" s="20"/>
-      <c r="O43" s="20"/>
-      <c r="P43" s="20"/>
-      <c r="Q43" s="20"/>
-      <c r="R43" s="20"/>
-      <c r="S43" s="20"/>
-      <c r="T43" s="20"/>
-      <c r="U43" s="20"/>
-      <c r="V43" s="20"/>
-      <c r="W43" s="20"/>
-      <c r="X43" s="20"/>
-      <c r="Z43" s="2"/>
+      <c r="AB10" s="14"/>
+      <c r="AC10" s="14"/>
+    </row>
+    <row r="11" spans="1:29" s="15" customFormat="1" ht="24" customHeight="1">
+      <c r="A11" s="21"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="22"/>
+      <c r="L11" s="22"/>
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="22"/>
+      <c r="R11" s="22"/>
+      <c r="S11" s="22"/>
+      <c r="T11" s="22"/>
+      <c r="U11" s="21"/>
+      <c r="V11" s="21"/>
+      <c r="W11" s="21"/>
+      <c r="X11" s="21"/>
+      <c r="AB11" s="14"/>
+      <c r="AC11" s="14"/>
+    </row>
+    <row r="12" spans="1:29" s="15" customFormat="1" ht="24" customHeight="1">
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="19"/>
+      <c r="V12" s="19"/>
+      <c r="W12" s="19"/>
+      <c r="X12" s="19"/>
+    </row>
+    <row r="13" spans="1:29" s="15" customFormat="1" ht="24" customHeight="1">
+      <c r="A13" s="14"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="19"/>
+      <c r="U13" s="19"/>
+      <c r="V13" s="19"/>
+      <c r="W13" s="19"/>
+      <c r="X13" s="19"/>
+    </row>
+    <row r="14" spans="1:29" s="15" customFormat="1" ht="24" customHeight="1">
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="19"/>
+      <c r="S14" s="19"/>
+      <c r="T14" s="19"/>
+      <c r="U14" s="19"/>
+      <c r="V14" s="19"/>
+      <c r="W14" s="19"/>
+      <c r="X14" s="19"/>
+    </row>
+    <row r="15" spans="1:29" s="15" customFormat="1" ht="24" customHeight="1">
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="19"/>
+      <c r="M15" s="19"/>
+      <c r="N15" s="19"/>
+      <c r="O15" s="19"/>
+      <c r="P15" s="19"/>
+      <c r="Q15" s="19"/>
+      <c r="R15" s="19"/>
+      <c r="S15" s="19"/>
+      <c r="T15" s="19"/>
+      <c r="U15" s="19"/>
+      <c r="V15" s="19"/>
+      <c r="W15" s="19"/>
+      <c r="X15" s="19"/>
+    </row>
+    <row r="16" spans="1:29" s="15" customFormat="1" ht="24" customHeight="1">
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="19"/>
+      <c r="O16" s="19"/>
+      <c r="P16" s="19"/>
+      <c r="Q16" s="19"/>
+      <c r="R16" s="19"/>
+      <c r="S16" s="19"/>
+      <c r="T16" s="19"/>
+      <c r="U16" s="19"/>
+      <c r="V16" s="19"/>
+      <c r="W16" s="19"/>
+      <c r="X16" s="19"/>
+    </row>
+    <row r="17" spans="1:28" s="15" customFormat="1" ht="24" customHeight="1">
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="19"/>
+      <c r="M17" s="19"/>
+      <c r="N17" s="19"/>
+      <c r="O17" s="19"/>
+      <c r="P17" s="19"/>
+      <c r="Q17" s="19"/>
+      <c r="R17" s="19"/>
+      <c r="S17" s="19"/>
+      <c r="T17" s="19"/>
+      <c r="U17" s="19"/>
+      <c r="V17" s="19"/>
+      <c r="W17" s="19"/>
+      <c r="X17" s="19"/>
+    </row>
+    <row r="18" spans="1:28" s="15" customFormat="1" ht="24" customHeight="1">
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="19"/>
+      <c r="P18" s="19"/>
+      <c r="Q18" s="19"/>
+      <c r="R18" s="19"/>
+      <c r="S18" s="19"/>
+      <c r="T18" s="19"/>
+      <c r="U18" s="19"/>
+      <c r="V18" s="19"/>
+      <c r="W18" s="19"/>
+      <c r="X18" s="19"/>
+    </row>
+    <row r="19" spans="1:28" s="15" customFormat="1" ht="24" customHeight="1">
+      <c r="M19" s="19"/>
+      <c r="N19" s="19"/>
+      <c r="O19" s="19"/>
+      <c r="P19" s="19"/>
+      <c r="Q19" s="19"/>
+      <c r="R19" s="19"/>
+      <c r="S19" s="19"/>
+      <c r="T19" s="19"/>
+      <c r="U19" s="19"/>
+      <c r="V19" s="19"/>
+      <c r="W19" s="19"/>
+      <c r="X19" s="19"/>
+      <c r="AB19" s="30"/>
+    </row>
+    <row r="20" spans="1:28" s="15" customFormat="1" ht="24" customHeight="1">
+      <c r="M20" s="19"/>
+      <c r="N20" s="19"/>
+      <c r="O20" s="19"/>
+      <c r="P20" s="19"/>
+      <c r="Q20" s="19"/>
+      <c r="R20" s="19"/>
+      <c r="S20" s="19"/>
+      <c r="T20" s="19"/>
+      <c r="U20" s="19"/>
+      <c r="V20" s="19"/>
+      <c r="W20" s="19"/>
+      <c r="X20" s="19"/>
+    </row>
+    <row r="21" spans="1:28" s="15" customFormat="1" ht="24" customHeight="1">
+      <c r="M21" s="19"/>
+      <c r="N21" s="19"/>
+      <c r="O21" s="19"/>
+      <c r="P21" s="19"/>
+      <c r="Q21" s="19"/>
+      <c r="R21" s="19"/>
+      <c r="S21" s="19"/>
+      <c r="T21" s="19"/>
+      <c r="U21" s="19"/>
+      <c r="V21" s="19"/>
+      <c r="W21" s="19"/>
+      <c r="X21" s="19"/>
+    </row>
+    <row r="22" spans="1:28" s="15" customFormat="1" ht="24" customHeight="1">
+      <c r="M22" s="19"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="19"/>
+      <c r="P22" s="19"/>
+      <c r="Q22" s="19"/>
+      <c r="R22" s="19"/>
+      <c r="S22" s="19"/>
+      <c r="T22" s="19"/>
+      <c r="U22" s="19"/>
+      <c r="V22" s="19"/>
+      <c r="W22" s="19"/>
+      <c r="X22" s="19"/>
+    </row>
+    <row r="23" spans="1:28" s="15" customFormat="1" ht="24" customHeight="1">
+      <c r="M23" s="19"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="19"/>
+      <c r="P23" s="19"/>
+      <c r="Q23" s="19"/>
+      <c r="R23" s="19"/>
+      <c r="S23" s="19"/>
+      <c r="T23" s="19"/>
+      <c r="U23" s="19"/>
+      <c r="V23" s="19"/>
+      <c r="W23" s="19"/>
+      <c r="X23" s="19"/>
+    </row>
+    <row r="24" spans="1:28" s="15" customFormat="1" ht="24" customHeight="1">
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19"/>
+      <c r="P24" s="19"/>
+      <c r="Q24" s="19"/>
+      <c r="R24" s="19"/>
+      <c r="S24" s="19"/>
+      <c r="T24" s="19"/>
+      <c r="U24" s="19"/>
+      <c r="V24" s="19"/>
+      <c r="W24" s="19"/>
+      <c r="X24" s="19"/>
+    </row>
+    <row r="25" spans="1:28" s="15" customFormat="1" ht="24" customHeight="1"/>
+    <row r="26" spans="1:28" s="15" customFormat="1" ht="24" customHeight="1">
+      <c r="A26" s="14"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="14"/>
+      <c r="L26" s="14"/>
+      <c r="M26" s="14"/>
+      <c r="N26" s="14"/>
+      <c r="O26" s="14"/>
+      <c r="P26" s="14"/>
+      <c r="Q26" s="14"/>
+      <c r="R26" s="14"/>
+      <c r="S26" s="14"/>
+      <c r="T26" s="14"/>
+      <c r="U26" s="14"/>
+      <c r="V26" s="14"/>
+      <c r="W26" s="14"/>
+      <c r="X26" s="14"/>
+    </row>
+    <row r="27" spans="1:28" s="15" customFormat="1" ht="24" customHeight="1">
+      <c r="A27" s="18"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="18"/>
+      <c r="K27" s="18"/>
+      <c r="L27" s="18"/>
+      <c r="M27" s="18"/>
+      <c r="N27" s="18"/>
+      <c r="O27" s="18"/>
+      <c r="P27" s="18"/>
+      <c r="Q27" s="18"/>
+      <c r="R27" s="18"/>
+      <c r="S27" s="18"/>
+      <c r="T27" s="18"/>
+      <c r="U27" s="18"/>
+      <c r="V27" s="18"/>
+      <c r="W27" s="18"/>
+      <c r="X27" s="18"/>
+      <c r="Z27" s="20"/>
+    </row>
+    <row r="28" spans="1:28" s="15" customFormat="1" ht="24" customHeight="1"/>
+    <row r="29" spans="1:28" s="15" customFormat="1" ht="24" customHeight="1"/>
+    <row r="30" spans="1:28" s="15" customFormat="1" ht="24" customHeight="1"/>
+    <row r="31" spans="1:28" s="15" customFormat="1" ht="24" customHeight="1"/>
+    <row r="32" spans="1:28" s="15" customFormat="1" ht="24" customHeight="1"/>
+    <row r="33" spans="1:26" s="15" customFormat="1" ht="24" customHeight="1"/>
+    <row r="34" spans="1:26" s="15" customFormat="1" ht="24" customHeight="1"/>
+    <row r="35" spans="1:26" s="7" customFormat="1" ht="24" customHeight="1">
+      <c r="A35" s="15"/>
+      <c r="B35" s="15"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="15"/>
+      <c r="J35" s="15"/>
+      <c r="K35" s="15"/>
+      <c r="L35" s="15"/>
+      <c r="M35" s="15"/>
+      <c r="N35" s="15"/>
+      <c r="O35" s="15"/>
+      <c r="P35" s="15"/>
+      <c r="Q35" s="15"/>
+      <c r="R35" s="15"/>
+      <c r="S35" s="15"/>
+      <c r="T35" s="15"/>
+      <c r="U35" s="15"/>
+      <c r="V35" s="15"/>
+      <c r="W35" s="15"/>
+      <c r="X35" s="15"/>
+    </row>
+    <row r="36" spans="1:26" s="7" customFormat="1" ht="24" customHeight="1">
+      <c r="A36" s="15"/>
+      <c r="B36" s="15"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="15"/>
+      <c r="J36" s="15"/>
+      <c r="K36" s="15"/>
+      <c r="L36" s="15"/>
+      <c r="M36" s="15"/>
+      <c r="N36" s="15"/>
+      <c r="O36" s="15"/>
+      <c r="P36" s="15"/>
+      <c r="Q36" s="15"/>
+      <c r="R36" s="15"/>
+      <c r="S36" s="15"/>
+      <c r="T36" s="15"/>
+      <c r="U36" s="15"/>
+      <c r="V36" s="15"/>
+      <c r="W36" s="15"/>
+      <c r="X36" s="15"/>
+    </row>
+    <row r="37" spans="1:26" ht="24" customHeight="1">
+      <c r="A37" s="18"/>
+      <c r="B37" s="18"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="18"/>
+      <c r="J37" s="18"/>
+      <c r="K37" s="18"/>
+      <c r="L37" s="18"/>
+      <c r="M37" s="18"/>
+      <c r="N37" s="18"/>
+      <c r="O37" s="18"/>
+      <c r="P37" s="18"/>
+      <c r="Q37" s="18"/>
+      <c r="R37" s="18"/>
+      <c r="S37" s="18"/>
+      <c r="T37" s="18"/>
+      <c r="U37" s="18"/>
+      <c r="V37" s="18"/>
+      <c r="W37" s="18"/>
+      <c r="X37" s="18"/>
+      <c r="Z37" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="22">
+    <mergeCell ref="O9:P9"/>
+    <mergeCell ref="Q9:X9"/>
+    <mergeCell ref="E10:N10"/>
+    <mergeCell ref="O10:P10"/>
+    <mergeCell ref="Q10:X10"/>
     <mergeCell ref="Q6:X6"/>
-    <mergeCell ref="M7:P7"/>
-    <mergeCell ref="Q7:X7"/>
-    <mergeCell ref="A9:X9"/>
+    <mergeCell ref="A8:X8"/>
     <mergeCell ref="A3:X3"/>
     <mergeCell ref="E4:X4"/>
     <mergeCell ref="M5:P5"/>
     <mergeCell ref="Q5:X5"/>
     <mergeCell ref="M6:P6"/>
-    <mergeCell ref="E10:T10"/>
-    <mergeCell ref="U10:X10"/>
-    <mergeCell ref="E11:T11"/>
-    <mergeCell ref="U11:X11"/>
-    <mergeCell ref="A13:L13"/>
-    <mergeCell ref="M13:X13"/>
-    <mergeCell ref="A14:L17"/>
-    <mergeCell ref="M14:X17"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="E9:N9"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="E5:L5"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="E6:L6"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="E7:L7"/>
-    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="F1:S2"/>
     <mergeCell ref="A1:E2"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="Z2:Z43" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="Z2:Z37" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"머리말,꼬리말,열머리,그룹머리,반복,그룹꼬리,합계"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2118,13 +1969,13 @@
     </row>
     <row r="3" spans="1:5" ht="20">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -2135,13 +1986,13 @@
     </row>
     <row r="4" spans="1:5" ht="20">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -2149,10 +2000,10 @@
     </row>
     <row r="5" spans="1:5" ht="20">
       <c r="A5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C5" t="s">
         <v>11</v>
@@ -2163,10 +2014,10 @@
     </row>
     <row r="6" spans="1:5" ht="20">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C6" t="s">
         <v>11</v>
@@ -2177,10 +2028,10 @@
     </row>
     <row r="7" spans="1:5" ht="20">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C7" t="s">
         <v>11</v>
@@ -2191,10 +2042,10 @@
     </row>
     <row r="8" spans="1:5" ht="20">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C8" t="s">
         <v>11</v>
@@ -2205,10 +2056,10 @@
     </row>
     <row r="9" spans="1:5" ht="20">
       <c r="A9" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C9" t="s">
         <v>11</v>
@@ -2219,10 +2070,10 @@
     </row>
     <row r="10" spans="1:5" ht="20">
       <c r="A10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C10" t="s">
         <v>11</v>
@@ -2236,10 +2087,10 @@
     </row>
     <row r="11" spans="1:5" ht="20">
       <c r="A11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C11" t="s">
         <v>11</v>
@@ -2253,13 +2104,13 @@
     </row>
     <row r="12" spans="1:5" ht="20">
       <c r="A12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D12" t="s">
         <v>10</v>
@@ -2270,29 +2121,29 @@
     </row>
     <row r="13" spans="1:5" ht="20">
       <c r="A13" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="20">
       <c r="A14" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B14" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="20">
       <c r="A15" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s">
         <v>9</v>

--- a/public/kk-baljooseo.xlsx
+++ b/public/kk-baljooseo.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10802"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D1FB09B-969A-AF48-B0B9-8683A5D5B668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57B25649-DF17-4D4A-B2A5-883568A43BE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13660" yWindow="720" windowWidth="38400" windowHeight="19060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13660" yWindow="720" windowWidth="38400" windowHeight="19060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="양식" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="75">
   <si>
     <t>{{발행처로고}}</t>
   </si>
@@ -158,30 +158,14 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>시공팀</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>시공일</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>발주담당자</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>연락처</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>현장주소</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>출입정보</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>부속</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -194,14 +178,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>시공팀 요청사항</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>케이산업 요청사항</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>품목</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -234,22 +210,14 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
+    <t>ㅈ</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
     <t>숫자</t>
   </si>
   <si>
-    <t>시공팀요청</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>여러 줄</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>케이산업요청</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>여러줄</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
@@ -1153,7 +1121,7 @@
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
       <c r="F1" s="16" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G1" s="16"/>
       <c r="H1" s="16"/>
@@ -1233,13 +1201,13 @@
     </row>
     <row r="4" spans="1:29" s="7" customFormat="1" ht="24" customHeight="1">
       <c r="A4" s="9" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
       <c r="E4" s="32" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F4" s="32"/>
       <c r="G4" s="32"/>
@@ -1263,13 +1231,13 @@
     </row>
     <row r="5" spans="1:29" s="7" customFormat="1" ht="24" customHeight="1">
       <c r="A5" s="11" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
       <c r="E5" s="31" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="F5" s="31"/>
       <c r="G5" s="31"/>
@@ -1279,13 +1247,13 @@
       <c r="K5" s="31"/>
       <c r="L5" s="31"/>
       <c r="M5" s="12" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="N5" s="12"/>
       <c r="O5" s="12"/>
       <c r="P5" s="12"/>
       <c r="Q5" s="31" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="R5" s="31"/>
       <c r="S5" s="31"/>
@@ -1298,13 +1266,13 @@
     </row>
     <row r="6" spans="1:29" s="7" customFormat="1" ht="24" customHeight="1">
       <c r="A6" s="11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
       <c r="D6" s="12"/>
       <c r="E6" s="31" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F6" s="31"/>
       <c r="G6" s="31"/>
@@ -1314,13 +1282,13 @@
       <c r="K6" s="31"/>
       <c r="L6" s="31"/>
       <c r="M6" s="12" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="N6" s="12"/>
       <c r="O6" s="12"/>
       <c r="P6" s="12"/>
       <c r="Q6" s="31" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="R6" s="31"/>
       <c r="S6" s="31"/>
@@ -1359,7 +1327,7 @@
     </row>
     <row r="8" spans="1:29" s="7" customFormat="1" ht="24" customHeight="1" thickBot="1">
       <c r="A8" s="13" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
@@ -1387,13 +1355,13 @@
     </row>
     <row r="9" spans="1:29" s="7" customFormat="1" ht="24" customHeight="1">
       <c r="A9" s="27" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B9" s="28"/>
       <c r="C9" s="28"/>
       <c r="D9" s="28"/>
       <c r="E9" s="35" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F9" s="36"/>
       <c r="G9" s="36"/>
@@ -1405,11 +1373,11 @@
       <c r="M9" s="36"/>
       <c r="N9" s="37"/>
       <c r="O9" s="35" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="P9" s="37"/>
       <c r="Q9" s="35" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="R9" s="36"/>
       <c r="S9" s="36"/>
@@ -1424,13 +1392,13 @@
     </row>
     <row r="10" spans="1:29" s="15" customFormat="1" ht="24" customHeight="1" thickBot="1">
       <c r="A10" s="25" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B10" s="26"/>
       <c r="C10" s="26"/>
       <c r="D10" s="26"/>
       <c r="E10" s="29" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="F10" s="39"/>
       <c r="G10" s="39"/>
@@ -1442,11 +1410,11 @@
       <c r="M10" s="39"/>
       <c r="N10" s="40"/>
       <c r="O10" s="44" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="P10" s="45"/>
       <c r="Q10" s="41" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="R10" s="42"/>
       <c r="S10" s="42"/>
@@ -1935,7 +1903,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1969,13 +1937,13 @@
     </row>
     <row r="3" spans="1:5" ht="20">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -1986,13 +1954,13 @@
     </row>
     <row r="4" spans="1:5" ht="20">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -2000,10 +1968,10 @@
     </row>
     <row r="5" spans="1:5" ht="20">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C5" t="s">
         <v>11</v>
@@ -2014,13 +1982,13 @@
     </row>
     <row r="6" spans="1:5" ht="20">
       <c r="A6" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -2028,10 +1996,10 @@
     </row>
     <row r="7" spans="1:5" ht="20">
       <c r="A7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C7" t="s">
         <v>11</v>
@@ -2042,10 +2010,10 @@
     </row>
     <row r="8" spans="1:5" ht="20">
       <c r="A8" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C8" t="s">
         <v>11</v>
@@ -2056,24 +2024,27 @@
     </row>
     <row r="9" spans="1:5" ht="20">
       <c r="A9" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
         <v>11</v>
       </c>
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="20">
       <c r="A10" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C10" t="s">
         <v>11</v>
@@ -2087,13 +2058,13 @@
     </row>
     <row r="11" spans="1:5" ht="20">
       <c r="A11" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="D11" t="s">
         <v>10</v>
@@ -2104,68 +2075,46 @@
     </row>
     <row r="12" spans="1:5" ht="20">
       <c r="A12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B12" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C12" t="s">
-        <v>65</v>
-      </c>
-      <c r="D12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="20">
       <c r="A13" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B13" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="20">
-      <c r="A14" t="s">
-        <v>68</v>
-      </c>
-      <c r="B14" t="s">
-        <v>56</v>
-      </c>
-      <c r="C14" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="20">
-      <c r="A15" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" t="s">
-        <v>9</v>
-      </c>
-    </row>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="20"/>
+    <row r="15" spans="1:5" ht="20"/>
     <row r="16" spans="1:5" ht="20"/>
-    <row r="17" ht="20"/>
-    <row r="18" ht="20"/>
-    <row r="19" ht="20"/>
-    <row r="20" ht="20"/>
-    <row r="21" ht="20"/>
-    <row r="22" ht="20"/>
-    <row r="23" ht="20"/>
-    <row r="24" ht="20"/>
-    <row r="25" ht="20"/>
-    <row r="26" ht="20"/>
-    <row r="27" ht="20"/>
-    <row r="28" ht="20"/>
-    <row r="29" ht="20"/>
-    <row r="30" ht="20"/>
-    <row r="31" ht="20"/>
-    <row r="32" ht="20"/>
+    <row r="17" spans="2:2" ht="20">
+      <c r="B17" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" ht="20"/>
+    <row r="19" spans="2:2" ht="20"/>
+    <row r="20" spans="2:2" ht="20"/>
+    <row r="21" spans="2:2" ht="20"/>
+    <row r="22" spans="2:2" ht="20"/>
+    <row r="23" spans="2:2" ht="20"/>
+    <row r="24" spans="2:2" ht="20"/>
+    <row r="25" spans="2:2" ht="20"/>
+    <row r="26" spans="2:2" ht="20"/>
+    <row r="27" spans="2:2" ht="20"/>
+    <row r="28" spans="2:2" ht="20"/>
+    <row r="29" spans="2:2" ht="20"/>
+    <row r="30" spans="2:2" ht="20"/>
+    <row r="31" spans="2:2" ht="20"/>
+    <row r="32" spans="2:2" ht="20"/>
     <row r="33" ht="20"/>
     <row r="34" ht="20"/>
     <row r="35" ht="20"/>
@@ -2180,16 +2129,13 @@
     <row r="44" ht="20"/>
     <row r="45" ht="20"/>
     <row r="46" ht="20"/>
-    <row r="47" ht="20"/>
-    <row r="48" ht="20"/>
-    <row r="49" ht="20"/>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="C2:C80" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C77" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"글자,숫자,금액,날짜,여러 줄,선택,예아니오,이미지"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D80" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D77" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"필수"</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/kk-baljooseo.xlsx
+++ b/public/kk-baljooseo.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10802"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57B25649-DF17-4D4A-B2A5-883568A43BE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A05E2FC-2F33-F04A-89CF-600BB0FFE363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13660" yWindow="720" windowWidth="38400" windowHeight="19060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="74">
   <si>
     <t>{{발행처로고}}</t>
   </si>
@@ -207,10 +207,6 @@
   </si>
   <si>
     <t>날짜</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㅈ</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
@@ -1121,7 +1117,7 @@
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
       <c r="F1" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G1" s="16"/>
       <c r="H1" s="16"/>
@@ -1231,13 +1227,13 @@
     </row>
     <row r="5" spans="1:29" s="7" customFormat="1" ht="24" customHeight="1">
       <c r="A5" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
       <c r="E5" s="31" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F5" s="31"/>
       <c r="G5" s="31"/>
@@ -1247,13 +1243,13 @@
       <c r="K5" s="31"/>
       <c r="L5" s="31"/>
       <c r="M5" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N5" s="12"/>
       <c r="O5" s="12"/>
       <c r="P5" s="12"/>
       <c r="Q5" s="31" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="R5" s="31"/>
       <c r="S5" s="31"/>
@@ -1282,13 +1278,13 @@
       <c r="K6" s="31"/>
       <c r="L6" s="31"/>
       <c r="M6" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N6" s="12"/>
       <c r="O6" s="12"/>
       <c r="P6" s="12"/>
       <c r="Q6" s="31" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R6" s="31"/>
       <c r="S6" s="31"/>
@@ -1327,7 +1323,7 @@
     </row>
     <row r="8" spans="1:29" s="7" customFormat="1" ht="24" customHeight="1" thickBot="1">
       <c r="A8" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
@@ -1373,11 +1369,11 @@
       <c r="M9" s="36"/>
       <c r="N9" s="37"/>
       <c r="O9" s="35" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P9" s="37"/>
       <c r="Q9" s="35" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R9" s="36"/>
       <c r="S9" s="36"/>
@@ -1410,11 +1406,11 @@
       <c r="M10" s="39"/>
       <c r="N10" s="40"/>
       <c r="O10" s="44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P10" s="45"/>
       <c r="Q10" s="41" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="R10" s="42"/>
       <c r="S10" s="42"/>
@@ -1937,10 +1933,10 @@
     </row>
     <row r="3" spans="1:5" ht="20">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
         <v>56</v>
@@ -1954,10 +1950,10 @@
     </row>
     <row r="4" spans="1:5" ht="20">
       <c r="A4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
         <v>58</v>
@@ -1982,10 +1978,10 @@
     </row>
     <row r="6" spans="1:5" ht="20">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C6" t="s">
         <v>58</v>
@@ -2064,7 +2060,7 @@
         <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D11" t="s">
         <v>10</v>
@@ -2075,7 +2071,7 @@
     </row>
     <row r="12" spans="1:5" ht="20">
       <c r="A12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
         <v>9</v>
@@ -2083,38 +2079,34 @@
     </row>
     <row r="13" spans="1:5" ht="20">
       <c r="A13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="20"/>
     <row r="15" spans="1:5" ht="20"/>
     <row r="16" spans="1:5" ht="20"/>
-    <row r="17" spans="2:2" ht="20">
-      <c r="B17" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2" ht="20"/>
-    <row r="19" spans="2:2" ht="20"/>
-    <row r="20" spans="2:2" ht="20"/>
-    <row r="21" spans="2:2" ht="20"/>
-    <row r="22" spans="2:2" ht="20"/>
-    <row r="23" spans="2:2" ht="20"/>
-    <row r="24" spans="2:2" ht="20"/>
-    <row r="25" spans="2:2" ht="20"/>
-    <row r="26" spans="2:2" ht="20"/>
-    <row r="27" spans="2:2" ht="20"/>
-    <row r="28" spans="2:2" ht="20"/>
-    <row r="29" spans="2:2" ht="20"/>
-    <row r="30" spans="2:2" ht="20"/>
-    <row r="31" spans="2:2" ht="20"/>
-    <row r="32" spans="2:2" ht="20"/>
+    <row r="17" ht="20"/>
+    <row r="18" ht="20"/>
+    <row r="19" ht="20"/>
+    <row r="20" ht="20"/>
+    <row r="21" ht="20"/>
+    <row r="22" ht="20"/>
+    <row r="23" ht="20"/>
+    <row r="24" ht="20"/>
+    <row r="25" ht="20"/>
+    <row r="26" ht="20"/>
+    <row r="27" ht="20"/>
+    <row r="28" ht="20"/>
+    <row r="29" ht="20"/>
+    <row r="30" ht="20"/>
+    <row r="31" ht="20"/>
+    <row r="32" ht="20"/>
     <row r="33" ht="20"/>
     <row r="34" ht="20"/>
     <row r="35" ht="20"/>

--- a/public/kk-baljooseo.xlsx
+++ b/public/kk-baljooseo.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10802"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A05E2FC-2F33-F04A-89CF-600BB0FFE363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FCAB021-B414-864B-8142-FCF1C3D0B23A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13660" yWindow="720" windowWidth="38400" windowHeight="19060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="3280" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="양식" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="72">
   <si>
     <t>{{발행처로고}}</t>
   </si>
@@ -190,6 +190,10 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
+    <t>{{부속.개수}}</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
     <t>{{현장주소}}</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -202,10 +206,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">부속 </t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>날짜</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -253,15 +253,7 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>수량</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>비고</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{부속.수량}}</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
@@ -1203,7 +1195,7 @@
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
       <c r="E4" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F4" s="32"/>
       <c r="G4" s="32"/>
@@ -1268,7 +1260,7 @@
       <c r="C6" s="12"/>
       <c r="D6" s="12"/>
       <c r="E6" s="31" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F6" s="31"/>
       <c r="G6" s="31"/>
@@ -1369,11 +1361,11 @@
       <c r="M9" s="36"/>
       <c r="N9" s="37"/>
       <c r="O9" s="35" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="P9" s="37"/>
       <c r="Q9" s="35" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R9" s="36"/>
       <c r="S9" s="36"/>
@@ -1406,11 +1398,11 @@
       <c r="M10" s="39"/>
       <c r="N10" s="40"/>
       <c r="O10" s="44" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="P10" s="45"/>
       <c r="Q10" s="41" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="R10" s="42"/>
       <c r="S10" s="42"/>
@@ -1899,7 +1891,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1939,7 +1931,7 @@
         <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -2006,24 +1998,27 @@
     </row>
     <row r="8" spans="1:5" ht="20">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C8" t="s">
         <v>11</v>
       </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="20">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C9" t="s">
         <v>11</v>
@@ -2032,62 +2027,49 @@
         <v>10</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="20">
       <c r="A10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="D10" t="s">
         <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="20">
       <c r="A11" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C11" t="s">
-        <v>59</v>
-      </c>
-      <c r="D11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="20">
       <c r="A12" t="s">
-        <v>61</v>
+        <v>70</v>
+      </c>
+      <c r="B12" t="s">
+        <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="20">
-      <c r="A13" t="s">
-        <v>71</v>
-      </c>
-      <c r="B13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13" t="s">
         <v>60</v>
       </c>
-    </row>
+      <c r="E12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="20"/>
     <row r="14" spans="1:5" ht="20"/>
     <row r="15" spans="1:5" ht="20"/>
     <row r="16" spans="1:5" ht="20"/>
@@ -2120,14 +2102,13 @@
     <row r="43" ht="20"/>
     <row r="44" ht="20"/>
     <row r="45" ht="20"/>
-    <row r="46" ht="20"/>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="C2:C77" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C76" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"글자,숫자,금액,날짜,여러 줄,선택,예아니오,이미지"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D77" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D76" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"필수"</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/kk-baljooseo.xlsx
+++ b/public/kk-baljooseo.xlsx
@@ -587,7 +587,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -698,6 +698,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1044,7 +1045,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC60"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.83203125" customHeight="1"/>
   <cols>
     <col min="1" max="24" width="4" customWidth="1"/>
@@ -1084,7 +1085,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" ht="24" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1110,7 +1111,7 @@
       <c r="W2" s="3"/>
       <c r="X2" s="3"/>
     </row>
-    <row r="3" ht="24" customHeight="1" spans="1:24" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="24" customHeight="1" spans="1:26" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>3</v>
       </c>
@@ -1137,8 +1138,9 @@
       <c r="V3" s="6"/>
       <c r="W3" s="6"/>
       <c r="X3" s="6"/>
-    </row>
-    <row r="4" ht="24" customHeight="1" spans="1:24" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z3" s="5"/>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:26" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>4</v>
       </c>
@@ -1167,6 +1169,7 @@
       <c r="V4" s="9"/>
       <c r="W4" s="9"/>
       <c r="X4" s="10"/>
+      <c r="Z4" s="5"/>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:26" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
@@ -1203,7 +1206,7 @@
       <c r="X5" s="14"/>
       <c r="Z5" s="5"/>
     </row>
-    <row r="6" ht="24" customHeight="1" spans="1:24" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="24" customHeight="1" spans="1:26" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>10</v>
       </c>
@@ -1236,6 +1239,7 @@
       <c r="V6" s="13"/>
       <c r="W6" s="13"/>
       <c r="X6" s="14"/>
+      <c r="Z6" s="5"/>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15"/>
@@ -1262,9 +1266,10 @@
       <c r="V7" s="16"/>
       <c r="W7" s="16"/>
       <c r="X7" s="16"/>
+      <c r="Z7" s="5"/>
       <c r="AC7" s="5"/>
     </row>
-    <row r="8" ht="24" customHeight="1" spans="1:24" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="24" customHeight="1" spans="1:26" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>14</v>
       </c>
@@ -1291,6 +1296,7 @@
       <c r="V8" s="6"/>
       <c r="W8" s="6"/>
       <c r="X8" s="6"/>
+      <c r="Z8" s="5"/>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:26" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
@@ -1393,10 +1399,11 @@
       <c r="V11" s="33"/>
       <c r="W11" s="33"/>
       <c r="X11" s="33"/>
+      <c r="Z11" s="16"/>
       <c r="AB11" s="16"/>
       <c r="AC11" s="16"/>
     </row>
-    <row r="12" ht="24" customHeight="1" spans="1:24" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="24" customHeight="1" spans="1:26" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="34"/>
       <c r="B12" s="34"/>
       <c r="C12" s="34"/>
@@ -1421,8 +1428,9 @@
       <c r="V12" s="34"/>
       <c r="W12" s="34"/>
       <c r="X12" s="34"/>
-    </row>
-    <row r="13" ht="24" customHeight="1" spans="1:24" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z12" s="16"/>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="1:26" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="16"/>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -1447,8 +1455,9 @@
       <c r="V13" s="34"/>
       <c r="W13" s="34"/>
       <c r="X13" s="34"/>
-    </row>
-    <row r="14" ht="24" customHeight="1" spans="1:24" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z13" s="16"/>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:26" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="34"/>
       <c r="B14" s="34"/>
       <c r="C14" s="34"/>
@@ -1473,8 +1482,9 @@
       <c r="V14" s="34"/>
       <c r="W14" s="34"/>
       <c r="X14" s="34"/>
-    </row>
-    <row r="15" ht="24" customHeight="1" spans="1:24" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z14" s="16"/>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:26" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="34"/>
       <c r="B15" s="34"/>
       <c r="C15" s="34"/>
@@ -1499,8 +1509,9 @@
       <c r="V15" s="34"/>
       <c r="W15" s="34"/>
       <c r="X15" s="34"/>
-    </row>
-    <row r="16" ht="24" customHeight="1" spans="1:24" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z15" s="16"/>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:26" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="34"/>
       <c r="B16" s="34"/>
       <c r="C16" s="34"/>
@@ -1525,8 +1536,9 @@
       <c r="V16" s="34"/>
       <c r="W16" s="34"/>
       <c r="X16" s="34"/>
-    </row>
-    <row r="17" ht="24" customHeight="1" spans="1:24" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z16" s="16"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" spans="1:26" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="34"/>
       <c r="B17" s="34"/>
       <c r="C17" s="34"/>
@@ -1551,8 +1563,9 @@
       <c r="V17" s="34"/>
       <c r="W17" s="34"/>
       <c r="X17" s="34"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" spans="1:24" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z17" s="16"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:26" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="34"/>
       <c r="B18" s="34"/>
       <c r="C18" s="34"/>
@@ -1577,6 +1590,7 @@
       <c r="V18" s="34"/>
       <c r="W18" s="34"/>
       <c r="X18" s="34"/>
+      <c r="Z18" s="16"/>
     </row>
     <row r="19" ht="24" customHeight="1" spans="13:28" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="M19" s="34"/>
@@ -1591,9 +1605,10 @@
       <c r="V19" s="34"/>
       <c r="W19" s="34"/>
       <c r="X19" s="34"/>
+      <c r="Z19" s="16"/>
       <c r="AB19" s="35"/>
     </row>
-    <row r="20" ht="24" customHeight="1" spans="13:24" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="24" customHeight="1" spans="13:26" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="M20" s="34"/>
       <c r="N20" s="34"/>
       <c r="O20" s="34"/>
@@ -1606,8 +1621,9 @@
       <c r="V20" s="34"/>
       <c r="W20" s="34"/>
       <c r="X20" s="34"/>
-    </row>
-    <row r="21" ht="24" customHeight="1" spans="13:24" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z20" s="16"/>
+    </row>
+    <row r="21" ht="24" customHeight="1" spans="13:26" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="M21" s="34"/>
       <c r="N21" s="34"/>
       <c r="O21" s="34"/>
@@ -1620,8 +1636,9 @@
       <c r="V21" s="34"/>
       <c r="W21" s="34"/>
       <c r="X21" s="34"/>
-    </row>
-    <row r="22" ht="24" customHeight="1" spans="13:24" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z21" s="16"/>
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="13:26" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="M22" s="34"/>
       <c r="N22" s="34"/>
       <c r="O22" s="34"/>
@@ -1634,8 +1651,9 @@
       <c r="V22" s="34"/>
       <c r="W22" s="34"/>
       <c r="X22" s="34"/>
-    </row>
-    <row r="23" ht="24" customHeight="1" spans="13:24" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z22" s="16"/>
+    </row>
+    <row r="23" ht="24" customHeight="1" spans="13:26" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="M23" s="34"/>
       <c r="N23" s="34"/>
       <c r="O23" s="34"/>
@@ -1648,8 +1666,9 @@
       <c r="V23" s="34"/>
       <c r="W23" s="34"/>
       <c r="X23" s="34"/>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="13:24" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z23" s="16"/>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="13:26" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="M24" s="34"/>
       <c r="N24" s="34"/>
       <c r="O24" s="34"/>
@@ -1662,9 +1681,12 @@
       <c r="V24" s="34"/>
       <c r="W24" s="34"/>
       <c r="X24" s="34"/>
-    </row>
-    <row r="25" ht="24" customHeight="1" s="16" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="26" ht="24" customHeight="1" spans="1:24" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z24" s="16"/>
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="26:26" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z25" s="16"/>
+    </row>
+    <row r="26" ht="24" customHeight="1" spans="1:26" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16"/>
       <c r="B26" s="16"/>
       <c r="C26" s="16"/>
@@ -1689,6 +1711,7 @@
       <c r="V26" s="16"/>
       <c r="W26" s="16"/>
       <c r="X26" s="16"/>
+      <c r="Z26" s="16"/>
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:26" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="36"/>
@@ -1717,18 +1740,28 @@
       <c r="X27" s="36"/>
       <c r="Z27" s="37"/>
     </row>
-    <row r="28" ht="24" customHeight="1" s="16" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="29" ht="24" customHeight="1" s="16" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="30" ht="24" customHeight="1" s="16" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="24" customHeight="1" spans="26:26" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z28" s="16"/>
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="26:26" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z29" s="16"/>
+    </row>
+    <row r="30" ht="24" customHeight="1" spans="26:26" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z30" s="16"/>
+    </row>
     <row r="31" ht="24" customHeight="1" spans="26:26" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="Z31" s="38" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="32" ht="24" customHeight="1" s="16" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="33" ht="24" customHeight="1" s="16" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="34" ht="24" customHeight="1" s="16" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="35" ht="24" customHeight="1" spans="1:24" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z31" s="38"/>
+    </row>
+    <row r="32" ht="24" customHeight="1" spans="26:26" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z32" s="16"/>
+    </row>
+    <row r="33" ht="24" customHeight="1" spans="26:26" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z33" s="16"/>
+    </row>
+    <row r="34" ht="24" customHeight="1" spans="26:26" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z34" s="16"/>
+    </row>
+    <row r="35" ht="24" customHeight="1" spans="1:26" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="16"/>
       <c r="B35" s="16"/>
       <c r="C35" s="16"/>
@@ -1753,8 +1786,9 @@
       <c r="V35" s="16"/>
       <c r="W35" s="16"/>
       <c r="X35" s="16"/>
-    </row>
-    <row r="36" ht="24" customHeight="1" spans="1:24" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z35" s="5"/>
+    </row>
+    <row r="36" ht="24" customHeight="1" spans="1:26" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="16"/>
       <c r="B36" s="16"/>
       <c r="C36" s="16"/>
@@ -1779,6 +1813,7 @@
       <c r="V36" s="16"/>
       <c r="W36" s="16"/>
       <c r="X36" s="16"/>
+      <c r="Z36" s="5"/>
     </row>
     <row r="37" ht="24" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A37" s="36"/>
@@ -1807,6 +1842,33 @@
       <c r="X37" s="36"/>
       <c r="Z37" s="39"/>
     </row>
+    <row r="38" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25">
+      <c r="Z42" s="40" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="43" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="26:26" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="22">
     <mergeCell ref="A1:E2"/>
@@ -1858,20 +1920,20 @@
     <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" spans="1:5" s="40" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
+    <row r="1" ht="15" customHeight="1" spans="1:5" s="41" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="40" t="s">
+      <c r="C1" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="40" t="s">
+      <c r="E1" s="41" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2088,219 +2150,219 @@
     <col min="2" max="2" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34.75" customHeight="1" spans="1:2" s="41" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="41" t="s">
+    <row r="1" ht="34.75" customHeight="1" spans="1:2" s="42" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="41" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1" spans="1:2" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="B2" s="42" t="s">
+      <c r="B1" s="42" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1" spans="1:2" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="43" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1" spans="1:2" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="42" t="s">
+    <row r="3" ht="24" customHeight="1" spans="1:2" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="43" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1" spans="1:2" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="42" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" ht="34.75" customHeight="1" spans="1:2" s="41" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="41" t="s">
+    <row r="4" ht="24" customHeight="1" spans="1:2" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="43" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" ht="34.75" customHeight="1" spans="1:2" s="42" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="41" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1" spans="1:2" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="42" t="s">
+      <c r="B5" s="42" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:2" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="43" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="7" ht="24" customHeight="1" spans="1:2" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="42" t="s">
+    <row r="7" ht="24" customHeight="1" spans="1:2" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="B7" s="42" t="s">
+      <c r="B7" s="43" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="8" ht="24" customHeight="1" spans="1:2" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="42" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" ht="34.75" customHeight="1" spans="1:2" s="41" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="41" t="s">
+    <row r="8" ht="24" customHeight="1" spans="1:2" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="43" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" ht="34.75" customHeight="1" spans="1:2" s="42" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="41" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1" spans="1:2" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="42" t="s">
+      <c r="B9" s="42" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1" spans="1:2" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="43" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="11" ht="24" customHeight="1" spans="1:2" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="42" t="s">
+    <row r="11" ht="24" customHeight="1" spans="1:2" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="B11" s="42" t="s">
+      <c r="B11" s="43" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="12" ht="24" customHeight="1" spans="1:2" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="42" t="s">
+    <row r="12" ht="24" customHeight="1" spans="1:2" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="B12" s="42" t="s">
+      <c r="B12" s="43" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="13" ht="24" customHeight="1" spans="1:2" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="42" t="s">
+    <row r="13" ht="24" customHeight="1" spans="1:2" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="43" t="s">
         <v>54</v>
       </c>
-      <c r="B13" s="42" t="s">
+      <c r="B13" s="43" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="14" ht="24" customHeight="1" spans="1:2" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="42" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" ht="34.75" customHeight="1" spans="1:2" s="41" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="41" t="s">
+    <row r="14" ht="24" customHeight="1" spans="1:2" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="43" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" ht="34.75" customHeight="1" spans="1:2" s="42" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="41" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1" spans="1:2" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="42" t="s">
+      <c r="B15" s="42" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:2" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="B16" s="42" t="s">
+      <c r="B16" s="43" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1" spans="1:2" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="42" t="s">
+    <row r="17" ht="24" customHeight="1" spans="1:2" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="42" t="s">
+      <c r="B17" s="43" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="18" ht="24" customHeight="1" spans="1:2" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="42" t="s">
+    <row r="18" ht="24" customHeight="1" spans="1:2" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="B18" s="42" t="s">
+      <c r="B18" s="43" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="19" ht="24" customHeight="1" spans="1:2" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="42" t="s">
+    <row r="19" ht="24" customHeight="1" spans="1:2" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="42" t="s">
+      <c r="B19" s="43" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="20" ht="24" customHeight="1" spans="1:2" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="42" t="s">
+    <row r="20" ht="24" customHeight="1" spans="1:2" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="B20" s="42" t="s">
+      <c r="B20" s="43" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="21" ht="24" customHeight="1" spans="1:2" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" s="42" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" ht="34.75" customHeight="1" spans="1:2" s="41" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="41" t="s">
+    <row r="21" ht="24" customHeight="1" spans="1:2" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="43" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" ht="34.75" customHeight="1" spans="1:2" s="42" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="B22" s="41" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" ht="24" customHeight="1" spans="1:2" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="B23" s="42" t="s">
+      <c r="B22" s="42" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1" spans="1:2" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="43" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="24" ht="24" customHeight="1" spans="1:2" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24" s="42" t="s">
+    <row r="24" ht="24" customHeight="1" spans="1:2" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="43" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="25" ht="24" customHeight="1" spans="1:2" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="42" t="s">
+    <row r="25" ht="24" customHeight="1" spans="1:2" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="43" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="26" ht="24" customHeight="1" spans="1:2" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="B26" s="42" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="27" ht="24" customHeight="1" spans="1:2" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="42" t="s">
+    <row r="26" ht="24" customHeight="1" spans="1:2" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="43" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1" spans="1:2" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="B27" s="42" t="s">
+      <c r="B27" s="43" t="s">
         <v>70</v>
       </c>
     </row>
